--- a/docs/oc-mensuales/gas-licuado-de-petroleo/sep-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/sep-2025.xlsx
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
